--- a/tests/fixtures/import/tc19-type-column-absent.xlsx
+++ b/tests/fixtures/import/tc19-type-column-absent.xlsx
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,6 +826,11 @@
           <t>Factor Status</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linked Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -861,6 +866,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>(status)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(URI)</t>
         </is>
       </c>
     </row>
